--- a/data/examples/ieee-9bus.xlsx
+++ b/data/examples/ieee-9bus.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Google Drive\PycharmProjects\prg-opf\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Google Drive\PycharmProjects\prg-opf\data\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D03D967-0957-41F9-8424-0FDC4025232B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE65E3B-5217-4A31-948A-AA3AAFFEBFFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="5280" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,8 +19,19 @@
     <sheet name="DC Lines" sheetId="4" r:id="rId4"/>
     <sheet name="Parameters" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -29,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="28">
   <si>
     <t>PR</t>
   </si>
@@ -67,70 +78,52 @@
     <t>Bus</t>
   </si>
   <si>
-    <t>B1</t>
-  </si>
-  <si>
-    <t>B2</t>
-  </si>
-  <si>
-    <t>B3</t>
-  </si>
-  <si>
-    <t>B4</t>
-  </si>
-  <si>
     <t>B5</t>
   </si>
   <si>
     <t>B6</t>
   </si>
   <si>
-    <t>B7</t>
+    <t>From_Port</t>
+  </si>
+  <si>
+    <t>To_Port</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Smax</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>Sbase</t>
+  </si>
+  <si>
+    <t>Vbase_squared</t>
+  </si>
+  <si>
+    <t>loss_c0</t>
+  </si>
+  <si>
+    <t>loss_c1</t>
+  </si>
+  <si>
+    <t>BigM</t>
+  </si>
+  <si>
+    <t>terminal_bus</t>
   </si>
   <si>
     <t>B8</t>
-  </si>
-  <si>
-    <t>B9</t>
-  </si>
-  <si>
-    <t>From_Port</t>
-  </si>
-  <si>
-    <t>To_Port</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>Smax</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>Sbase</t>
-  </si>
-  <si>
-    <t>Vbase_squared</t>
-  </si>
-  <si>
-    <t>loss_c0</t>
-  </si>
-  <si>
-    <t>loss_c1</t>
-  </si>
-  <si>
-    <t>BigM</t>
-  </si>
-  <si>
-    <t>terminal_bus</t>
   </si>
 </sst>
 </file>
@@ -493,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="12.88671875" bestFit="1" customWidth="1"/>
@@ -537,7 +530,7 @@
         <v>8</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>52900</v>
       </c>
       <c r="G2">
         <v>-5.8199999999999998E-5</v>
@@ -557,7 +550,7 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>52900</v>
       </c>
       <c r="G3">
         <v>-5.8199999999999998E-5</v>
@@ -577,7 +570,7 @@
         <v>9</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>52900</v>
       </c>
       <c r="G4">
         <v>-5.8199999999999998E-5</v>
@@ -588,16 +581,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>-5.8199999999999998E-5</v>
@@ -614,7 +604,10 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D6">
+        <v>52900</v>
       </c>
       <c r="G6">
         <v>-5.8199999999999998E-5</v>
@@ -631,10 +624,10 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>52900</v>
       </c>
       <c r="G7">
         <v>-5.8199999999999998E-5</v>
@@ -645,27 +638,24 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8">
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8">
         <v>10</v>
       </c>
       <c r="G8">
-        <v>-5.8199999999999998E-5</v>
+        <v>-2.3280000000000001E-5</v>
       </c>
       <c r="H8">
-        <v>1.5399999999999999E-3</v>
+        <v>6.1600000000000001E-4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9">
         <v>7</v>
@@ -674,7 +664,7 @@
         <v>8</v>
       </c>
       <c r="D9">
-        <v>36</v>
+        <v>52900</v>
       </c>
       <c r="G9">
         <v>-2.3280000000000001E-5</v>
@@ -697,83 +687,6 @@
         <v>-2.3280000000000001E-5</v>
       </c>
       <c r="H10">
-        <v>6.1600000000000001E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>3</v>
-      </c>
-      <c r="B11">
-        <v>9</v>
-      </c>
-      <c r="C11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>-2.3280000000000001E-5</v>
-      </c>
-      <c r="H11">
-        <v>6.1600000000000001E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>3</v>
-      </c>
-      <c r="B12">
-        <v>10</v>
-      </c>
-      <c r="C12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12">
-        <v>-2.3280000000000001E-5</v>
-      </c>
-      <c r="H12">
-        <v>6.1600000000000001E-4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>3</v>
-      </c>
-      <c r="B13">
-        <v>11</v>
-      </c>
-      <c r="C13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13">
-        <v>-2.3280000000000001E-5</v>
-      </c>
-      <c r="H13">
-        <v>6.1600000000000001E-4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>3</v>
-      </c>
-      <c r="B14">
-        <v>12</v>
-      </c>
-      <c r="C14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14">
-        <v>36</v>
-      </c>
-      <c r="G14">
-        <v>-2.3280000000000001E-5</v>
-      </c>
-      <c r="H14">
         <v>6.1600000000000001E-4</v>
       </c>
     </row>
@@ -784,7 +697,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
@@ -812,10 +725,16 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>26</v>
+      </c>
+      <c r="D2">
+        <v>125</v>
+      </c>
+      <c r="E2">
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -823,10 +742,10 @@
         <v>12</v>
       </c>
       <c r="B3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -834,16 +753,10 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4">
-        <v>0.27202871297791642</v>
-      </c>
-      <c r="E4">
-        <v>0.1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -851,10 +764,10 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -862,10 +775,10 @@
         <v>13</v>
       </c>
       <c r="B6">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -873,289 +786,55 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D7">
-        <v>0.27202871297791642</v>
+        <v>90</v>
       </c>
       <c r="E7">
-        <v>0.1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B8">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B9">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B10">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D10">
-        <v>0.27202871297791642</v>
+        <v>100</v>
       </c>
       <c r="E10">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12">
-        <v>23</v>
-      </c>
-      <c r="C12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12">
-        <v>0.81608613893374915</v>
-      </c>
-      <c r="E12">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13">
-        <v>24</v>
-      </c>
-      <c r="C13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14">
-        <v>25</v>
-      </c>
-      <c r="C14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15">
-        <v>26</v>
-      </c>
-      <c r="C15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16">
-        <v>27</v>
-      </c>
-      <c r="C16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16">
-        <v>0.81608613893374915</v>
-      </c>
-      <c r="E16">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17">
-        <v>28</v>
-      </c>
-      <c r="C17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18">
-        <v>29</v>
-      </c>
-      <c r="C18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19">
-        <v>30</v>
-      </c>
-      <c r="C19" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20">
-        <v>31</v>
-      </c>
-      <c r="C20" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21">
-        <v>32</v>
-      </c>
-      <c r="C21" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22">
-        <v>33</v>
-      </c>
-      <c r="C22" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22">
-        <v>0.81608613893374915</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23">
-        <v>34</v>
-      </c>
-      <c r="C23" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24">
         <v>35</v>
-      </c>
-      <c r="C24" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25">
-        <v>36</v>
-      </c>
-      <c r="C25" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25">
-        <v>0.81608613893374915</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26">
-        <v>37</v>
-      </c>
-      <c r="C26" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B27">
-        <v>38</v>
-      </c>
-      <c r="C27" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27">
-        <v>-0.57991040658668036</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>20</v>
-      </c>
-      <c r="B28">
-        <v>39</v>
-      </c>
-      <c r="C28" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1165,160 +844,126 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C2">
-        <v>0.48499999999999999</v>
+        <v>3.9E-2</v>
       </c>
       <c r="D2">
-        <v>0.78749999999999998</v>
+        <v>0.17</v>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>0.48499999999999999</v>
+        <v>1.9900000000000001E-2</v>
       </c>
       <c r="D3">
-        <v>0.78749999999999998</v>
+        <v>0.1008</v>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B4">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C4">
-        <v>0.48499999999999999</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="D4">
-        <v>0.78749999999999998</v>
+        <v>1.61E-2</v>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>0.48499999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="D5">
-        <v>0.78749999999999998</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>0.97</v>
+        <v>8.5000000000000006E-3</v>
       </c>
       <c r="D6">
-        <v>1.575</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="E6">
-        <v>100</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B7">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>0.97</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="D7">
-        <v>1.575</v>
+        <v>9.1999999999999998E-2</v>
       </c>
       <c r="E7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8">
-        <v>22</v>
-      </c>
-      <c r="C8">
-        <v>0.97</v>
-      </c>
-      <c r="D8">
-        <v>1.575</v>
-      </c>
-      <c r="E8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>24</v>
-      </c>
-      <c r="B9">
-        <v>10</v>
-      </c>
-      <c r="C9">
-        <v>0.97</v>
-      </c>
-      <c r="D9">
-        <v>1.575</v>
-      </c>
-      <c r="E9">
-        <v>100</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -1328,126 +973,24 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>28</v>
-      </c>
-      <c r="C2">
-        <v>0.64700000000000002</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>30</v>
-      </c>
-      <c r="B3">
-        <v>31</v>
-      </c>
-      <c r="C3">
-        <v>0.64700000000000002</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>32</v>
-      </c>
-      <c r="B4">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>0.64700000000000002</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>39</v>
-      </c>
-      <c r="C5">
-        <v>0.64700000000000002</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>37</v>
-      </c>
-      <c r="B6">
-        <v>35</v>
-      </c>
-      <c r="C6">
-        <v>0.64700000000000002</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>34</v>
-      </c>
-      <c r="B7">
-        <v>8</v>
-      </c>
-      <c r="C7">
-        <v>0.64700000000000002</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>100</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1462,15 +1005,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1478,7 +1021,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B3">
         <v>36</v>
@@ -1486,7 +1029,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>-5.8199999999999998E-5</v>
@@ -1494,7 +1037,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B5">
         <v>1.5399999999999999E-3</v>
@@ -1502,7 +1045,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B6">
         <v>999999999</v>
